--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_rezmat_a_2022.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_rezmat_a_2022.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:33</t>
+    <t xml:space="preserve">2026-09-24 01:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -640,7 +640,7 @@
         <v>-0.14</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11">
@@ -651,10 +651,10 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12">
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13">
@@ -679,10 +679,10 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14">
@@ -707,7 +707,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.09</v>
+        <v>-0.14</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>322</v>
@@ -735,7 +735,7 @@
         <v>22</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.19</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>322</v>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_rezmat_a_2022.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_rezmat_a_2022.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:24</t>
+    <t xml:space="preserve">2026-10-01 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_rezmat_a_2022.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_rezmat_a_2022.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:04</t>
+    <t xml:space="preserve">2026-10-05 19:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
